--- a/diseases/d099/1975-1979.xlsx
+++ b/diseases/d099/1975-1979.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">

--- a/diseases/d099/1975-1979.xlsx
+++ b/diseases/d099/1975-1979.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
